--- a/data/multiplicadores/multiplicadores_emprego.xlsx
+++ b/data/multiplicadores/multiplicadores_emprego.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7cfd6d076248aa8/Documents/Study/UFV/Mestrado/4º Semestre/ERU 799 - Pesquisa/Estimação/mip-energia/data/multiplicadores/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7cfd6d076248aa8/Documents/Study/UFV/Mestrado/4º Semestre (2025-2)/ERU 799 - Pesquisa/Estimação/mip-energia/data/multiplicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_2E298ED3D842400E62355476585DCE3A8747196D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83E67919-8AB7-428B-956A-A387DE94BDB1}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_2E298ED3D842400E62355476585DCE3A8747196D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20E9C094-D618-4A51-A38A-0B15EA8F42FA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -669,28 +669,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>6563436</v>
+        <v>6687599</v>
       </c>
       <c r="D2">
-        <v>74451</v>
+        <v>398037.00000000099</v>
       </c>
       <c r="E2">
-        <v>88.157795059838008</v>
+        <v>16.80145061891227</v>
       </c>
       <c r="F2">
-        <v>88.157795059838008</v>
+        <v>24.59708969007912</v>
       </c>
       <c r="G2">
-        <v>88157795.059838012</v>
+        <v>24597089.690079119</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>1.4639860716783479</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -721,730 +721,730 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>1122849</v>
+        <v>801096</v>
       </c>
       <c r="D4">
-        <v>40366.000000006599</v>
+        <v>37870.000000000036</v>
       </c>
       <c r="E4">
-        <v>27.816702175093312</v>
+        <v>21.153842091365181</v>
       </c>
       <c r="F4">
-        <v>29.432131767383229</v>
+        <v>22.774518074522991</v>
       </c>
       <c r="G4">
-        <v>29432131.767383229</v>
+        <v>22774518.074522991</v>
       </c>
       <c r="H4">
-        <v>1.058074087363827</v>
+        <v>1.07661378846254</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>4502808</v>
+        <v>118276</v>
       </c>
       <c r="D5">
-        <v>171919.00000001461</v>
+        <v>20011.000000000651</v>
       </c>
       <c r="E5">
-        <v>26.191450625001409</v>
+        <v>5.9105491979409388</v>
       </c>
       <c r="F5">
-        <v>34.493514780164503</v>
+        <v>6.5346297758702052</v>
       </c>
       <c r="G5">
-        <v>34493514.780164503</v>
+        <v>6534629.7758702049</v>
       </c>
       <c r="H5">
-        <v>1.316976110793888</v>
+        <v>1.1055875785868901</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>1676586</v>
+        <v>50144</v>
       </c>
       <c r="D6">
-        <v>66432.000000002095</v>
+        <v>225938</v>
       </c>
       <c r="E6">
-        <v>25.237626445085908</v>
+        <v>0.22193699156405741</v>
       </c>
       <c r="F6">
-        <v>30.661451509794151</v>
+        <v>6.8699275379572038</v>
       </c>
       <c r="G6">
-        <v>30661451.50979415</v>
+        <v>6869927.5379572036</v>
       </c>
       <c r="H6">
-        <v>1.214910268067793</v>
+        <v>30.954405074804061</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>801096</v>
+        <v>35440</v>
       </c>
       <c r="D7">
-        <v>37870.000000000036</v>
+        <v>92326.00000000032</v>
       </c>
       <c r="E7">
-        <v>21.153842091365181</v>
+        <v>0.38385720165500381</v>
       </c>
       <c r="F7">
-        <v>22.774518074522991</v>
+        <v>2.8433857853210549</v>
       </c>
       <c r="G7">
-        <v>22774518.074522991</v>
+        <v>2843385.785321055</v>
       </c>
       <c r="H7">
-        <v>1.07661378846254</v>
+        <v>7.4074050794456161</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>5622208</v>
+        <v>28949</v>
       </c>
       <c r="D8">
-        <v>276938.00000003021</v>
+        <v>18272.999999999829</v>
       </c>
       <c r="E8">
-        <v>20.301323761995061</v>
+        <v>1.584249986318627</v>
       </c>
       <c r="F8">
-        <v>30.069130255861079</v>
+        <v>2.1794480592359018</v>
       </c>
       <c r="G8">
-        <v>30069130.255861081</v>
+        <v>2179448.059235902</v>
       </c>
       <c r="H8">
-        <v>1.4811413584838129</v>
+        <v>1.3756970667870141</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>2878667</v>
+        <v>765202</v>
       </c>
       <c r="D9">
-        <v>143437.0000000103</v>
+        <v>292406.00000000309</v>
       </c>
       <c r="E9">
-        <v>20.069208084384041</v>
+        <v>2.616916205549789</v>
       </c>
       <c r="F9">
-        <v>23.524790409325259</v>
+        <v>38.621852550824357</v>
       </c>
       <c r="G9">
-        <v>23524790.409325261</v>
+        <v>38621852.550824367</v>
       </c>
       <c r="H9">
-        <v>1.1721832924553719</v>
+        <v>14.758536199560989</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>781913</v>
+        <v>156442</v>
       </c>
       <c r="D10">
-        <v>43096.000000001281</v>
+        <v>51555.000000003318</v>
       </c>
       <c r="E10">
-        <v>18.14351679970245</v>
+        <v>3.0344680438364842</v>
       </c>
       <c r="F10">
-        <v>18.663456218173771</v>
+        <v>5.6682965287302336</v>
       </c>
       <c r="G10">
-        <v>18663456.218173768</v>
+        <v>5668296.5287302341</v>
       </c>
       <c r="H10">
-        <v>1.028657036241168</v>
+        <v>1.867970414202746</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C11">
-        <v>2968849</v>
+        <v>1285134</v>
       </c>
       <c r="D11">
-        <v>175093.00000000029</v>
+        <v>324942.99999999697</v>
       </c>
       <c r="E11">
-        <v>16.955840610418431</v>
+        <v>3.954952099291297</v>
       </c>
       <c r="F11">
-        <v>21.756919884595071</v>
+        <v>19.72282493630215</v>
       </c>
       <c r="G11">
-        <v>21756919.88459507</v>
+        <v>19722824.936302152</v>
       </c>
       <c r="H11">
-        <v>1.2831519465467629</v>
+        <v>4.9868682201830863</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>6687599</v>
+        <v>190956</v>
       </c>
       <c r="D12">
-        <v>398037.00000000099</v>
+        <v>78544.000000008746</v>
       </c>
       <c r="E12">
-        <v>16.80145061891227</v>
+        <v>2.431197799958988</v>
       </c>
       <c r="F12">
-        <v>24.59708969007912</v>
+        <v>6.3531535615948442</v>
       </c>
       <c r="G12">
-        <v>24597089.690079119</v>
+        <v>6353153.5615948439</v>
       </c>
       <c r="H12">
-        <v>1.4639860716783479</v>
+        <v>2.6131783936716362</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="C13">
-        <v>4178701</v>
+        <v>17784</v>
       </c>
       <c r="D13">
-        <v>261715.00000003359</v>
+        <v>15694.00000000024</v>
       </c>
       <c r="E13">
-        <v>15.966608715585521</v>
+        <v>1.133171912832913</v>
       </c>
       <c r="F13">
-        <v>21.873105311559542</v>
+        <v>1.885871726459279</v>
       </c>
       <c r="G13">
-        <v>21873105.311559539</v>
+        <v>1885871.726459279</v>
       </c>
       <c r="H13">
-        <v>1.36992806056608</v>
+        <v>1.664241502195928</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C14">
-        <v>438611</v>
+        <v>632157</v>
       </c>
       <c r="D14">
-        <v>27787.00000000565</v>
+        <v>54793.000000011139</v>
       </c>
       <c r="E14">
-        <v>15.78475546118367</v>
+        <v>11.5371854068927</v>
       </c>
       <c r="F14">
-        <v>16.746911905795791</v>
+        <v>15.11078062950588</v>
       </c>
       <c r="G14">
-        <v>16746911.90579579</v>
+        <v>15110780.629505871</v>
       </c>
       <c r="H14">
-        <v>1.060954789383856</v>
+        <v>1.3097458432520459</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C15">
-        <v>16293655</v>
+        <v>1676586</v>
       </c>
       <c r="D15">
-        <v>1120579</v>
+        <v>66432.000000002095</v>
       </c>
       <c r="E15">
-        <v>14.54038938798603</v>
+        <v>25.237626445085908</v>
       </c>
       <c r="F15">
-        <v>44.922939518520081</v>
+        <v>30.661451509794151</v>
       </c>
       <c r="G15">
-        <v>44922939.51852008</v>
+        <v>30661451.50979415</v>
       </c>
       <c r="H15">
-        <v>3.0895279569086069</v>
+        <v>1.214910268067793</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="C16">
-        <v>7617875</v>
+        <v>468535</v>
       </c>
       <c r="D16">
-        <v>552073.00000004855</v>
+        <v>43848.000000000589</v>
       </c>
       <c r="E16">
-        <v>13.79867336384741</v>
+        <v>10.68543605181522</v>
       </c>
       <c r="F16">
-        <v>38.249635993911859</v>
+        <v>13.764999025546031</v>
       </c>
       <c r="G16">
-        <v>38249635.993911862</v>
+        <v>13764999.025546029</v>
       </c>
       <c r="H16">
-        <v>2.771979232012701</v>
+        <v>1.2882019001187761</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>4202039</v>
+        <v>376397</v>
       </c>
       <c r="D17">
-        <v>351095.00000001851</v>
+        <v>32687.000000022239</v>
       </c>
       <c r="E17">
-        <v>11.96838177701129</v>
+        <v>11.515189524879739</v>
       </c>
       <c r="F17">
-        <v>18.139004115683299</v>
+        <v>15.14496259976354</v>
       </c>
       <c r="G17">
-        <v>18139004.115683291</v>
+        <v>15144962.599763541</v>
       </c>
       <c r="H17">
-        <v>1.515576997261606</v>
+        <v>1.3152160949710221</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C18">
-        <v>632157</v>
+        <v>201777</v>
       </c>
       <c r="D18">
-        <v>54793.000000011139</v>
+        <v>109595.0000000502</v>
       </c>
       <c r="E18">
-        <v>11.5371854068927</v>
+        <v>1.841115014370251</v>
       </c>
       <c r="F18">
-        <v>15.11078062950588</v>
+        <v>8.1877465356174266</v>
       </c>
       <c r="G18">
-        <v>15110780.629505871</v>
+        <v>8187746.535617427</v>
       </c>
       <c r="H18">
-        <v>1.3097458432520459</v>
+        <v>4.4471673261640454</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>376397</v>
+        <v>180593</v>
       </c>
       <c r="D19">
-        <v>32687.000000022239</v>
+        <v>21333.000000031148</v>
       </c>
       <c r="E19">
-        <v>11.515189524879739</v>
+        <v>8.4654291473180674</v>
       </c>
       <c r="F19">
-        <v>15.14496259976354</v>
+        <v>9.4353582016754647</v>
       </c>
       <c r="G19">
-        <v>15144962.599763541</v>
+        <v>9435358.2016754653</v>
       </c>
       <c r="H19">
-        <v>1.3152160949710221</v>
+        <v>1.1145752964768101</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C20">
-        <v>3428002</v>
+        <v>18842.967499999999</v>
       </c>
       <c r="D20">
-        <v>302873.0000000092</v>
+        <v>433811.26648911083</v>
       </c>
       <c r="E20">
-        <v>11.3182819201444</v>
+        <v>4.3435864754040411E-2</v>
       </c>
       <c r="F20">
-        <v>19.43730073265084</v>
+        <v>10.384374421492151</v>
       </c>
       <c r="G20">
-        <v>19437300.732650839</v>
+        <v>10384374.42149215</v>
       </c>
       <c r="H20">
-        <v>1.717336683234238</v>
+        <v>239.07373504118371</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="C21">
-        <v>2218572</v>
+        <v>2617.3804999999988</v>
       </c>
       <c r="D21">
-        <v>202716.0000000016</v>
+        <v>10385.862128765169</v>
       </c>
       <c r="E21">
-        <v>10.944237258035789</v>
+        <v>0.25201379216760261</v>
       </c>
       <c r="F21">
-        <v>16.386950474223841</v>
+        <v>0.47391619658489198</v>
       </c>
       <c r="G21">
-        <v>16386950.474223839</v>
+        <v>473916.19658489199</v>
       </c>
       <c r="H21">
-        <v>1.497313160146611</v>
+        <v>1.8805169054783819</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>468535</v>
+        <v>260.65199999999999</v>
       </c>
       <c r="D22">
-        <v>43848.000000000589</v>
+        <v>3303.8713821240121</v>
       </c>
       <c r="E22">
-        <v>10.68543605181522</v>
+        <v>7.8892901645714344E-2</v>
       </c>
       <c r="F22">
-        <v>13.764999025546031</v>
+        <v>0.22889457121488879</v>
       </c>
       <c r="G22">
-        <v>13764999.025546029</v>
+        <v>228894.5712148888</v>
       </c>
       <c r="H22">
-        <v>1.2882019001187761</v>
+        <v>2.901332901187859</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C23">
-        <v>4076625</v>
+        <v>98255.000000000015</v>
       </c>
       <c r="D23">
-        <v>398813.04492834641</v>
+        <v>54637.000000001673</v>
       </c>
       <c r="E23">
-        <v>10.221894824760399</v>
+        <v>1.7983234804252981</v>
       </c>
       <c r="F23">
-        <v>21.240187552044389</v>
+        <v>4.4025505797584703</v>
       </c>
       <c r="G23">
-        <v>21240187.552044392</v>
+        <v>4402550.5797584699</v>
       </c>
       <c r="H23">
-        <v>2.0779109857982969</v>
+        <v>2.4481416317365108</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C24">
-        <v>630552</v>
+        <v>92285</v>
       </c>
       <c r="D24">
-        <v>62891.000000023807</v>
+        <v>179506</v>
       </c>
       <c r="E24">
-        <v>10.026108664192989</v>
+        <v>0.51410537809321133</v>
       </c>
       <c r="F24">
-        <v>11.67074224051405</v>
+        <v>5.7260149380359806</v>
       </c>
       <c r="G24">
-        <v>11670742.240514049</v>
+        <v>5726014.9380359817</v>
       </c>
       <c r="H24">
-        <v>1.164035083939861</v>
+        <v>11.13782345415926</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C25">
-        <v>744311</v>
+        <v>85311</v>
       </c>
       <c r="D25">
-        <v>75234.938746999134</v>
+        <v>88307.86977582956</v>
       </c>
       <c r="E25">
-        <v>9.8931561904101102</v>
+        <v>0.96606338955477977</v>
       </c>
       <c r="F25">
-        <v>14.622708703082379</v>
+        <v>3.7180230750651639</v>
       </c>
       <c r="G25">
-        <v>14622708.703082381</v>
+        <v>3718023.0750651639</v>
       </c>
       <c r="H25">
-        <v>1.478063059113212</v>
+        <v>3.8486326210732948</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C26">
-        <v>180593</v>
+        <v>137454</v>
       </c>
       <c r="D26">
-        <v>21333.000000031148</v>
+        <v>50175.904170072157</v>
       </c>
       <c r="E26">
-        <v>8.4654291473180674</v>
+        <v>2.739442413117203</v>
       </c>
       <c r="F26">
-        <v>9.4353582016754647</v>
+        <v>4.7715573064099273</v>
       </c>
       <c r="G26">
-        <v>9435358.2016754653</v>
+        <v>4771557.3064099271</v>
       </c>
       <c r="H26">
-        <v>1.1145752964768101</v>
+        <v>1.741798726471635</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="C27">
-        <v>1887743</v>
+        <v>104114</v>
       </c>
       <c r="D27">
-        <v>228613.00000000559</v>
+        <v>76244.0000000078</v>
       </c>
       <c r="E27">
-        <v>8.2573738151371661</v>
+        <v>1.3655369602852601</v>
       </c>
       <c r="F27">
-        <v>13.45227843684072</v>
+        <v>3.695716468085589</v>
       </c>
       <c r="G27">
-        <v>13452278.43684072</v>
+        <v>3695716.4680855889</v>
       </c>
       <c r="H27">
-        <v>1.6291231011221039</v>
+        <v>2.7064199472957191</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C28">
-        <v>136112</v>
+        <v>444627</v>
       </c>
       <c r="D28">
-        <v>17903.00000000689</v>
+        <v>121217.0000000571</v>
       </c>
       <c r="E28">
-        <v>7.6027481427664441</v>
+        <v>3.668025111987514</v>
       </c>
       <c r="F28">
-        <v>8.6565163276870987</v>
+        <v>7.9216015789728083</v>
       </c>
       <c r="G28">
-        <v>8656516.3276870996</v>
+        <v>7921601.5789728081</v>
       </c>
       <c r="H28">
-        <v>1.1386035897984139</v>
+        <v>2.1596366810805452</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C29">
-        <v>563905</v>
+        <v>563545</v>
       </c>
       <c r="D29">
-        <v>82219.993974276586</v>
+        <v>83887.9674075699</v>
       </c>
       <c r="E29">
-        <v>6.8584899212766146</v>
+        <v>6.7178287591832477</v>
       </c>
       <c r="F29">
-        <v>8.9024938057993062</v>
+        <v>11.395535851072591</v>
       </c>
       <c r="G29">
-        <v>8902493.8057993054</v>
+        <v>11395535.851072591</v>
       </c>
       <c r="H29">
-        <v>1.2980253536834281</v>
+        <v>1.696312344296502</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30">
-        <v>563545</v>
+        <v>122810</v>
       </c>
       <c r="D30">
-        <v>83887.9674075699</v>
+        <v>150065.03251769711</v>
       </c>
       <c r="E30">
-        <v>6.7178287591832477</v>
+        <v>0.81837852522716836</v>
       </c>
       <c r="F30">
-        <v>11.395535851072591</v>
+        <v>7.2253552226546507</v>
       </c>
       <c r="G30">
-        <v>11395535.851072591</v>
+        <v>7225355.2226546509</v>
       </c>
       <c r="H30">
-        <v>1.696312344296502</v>
+        <v>8.8288670828074469</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C31">
-        <v>532601</v>
+        <v>100208</v>
       </c>
       <c r="D31">
-        <v>79968.000000001339</v>
+        <v>73148.000000061249</v>
       </c>
       <c r="E31">
-        <v>6.6601765706281402</v>
+        <v>1.369934926449337</v>
       </c>
       <c r="F31">
-        <v>8.963063922635822</v>
+        <v>4.3521505475161097</v>
       </c>
       <c r="G31">
-        <v>8963063.9226358216</v>
+        <v>4352150.5475161094</v>
       </c>
       <c r="H31">
-        <v>1.345769714599397</v>
+        <v>3.176903124001826</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -1475,1100 +1475,1100 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="C33">
-        <v>298455</v>
+        <v>127233</v>
       </c>
       <c r="D33">
-        <v>48479.000000053493</v>
+        <v>103544.000000003</v>
       </c>
       <c r="E33">
-        <v>6.1563769879673824</v>
+        <v>1.2287819670864211</v>
       </c>
       <c r="F33">
-        <v>7.3989819115470503</v>
+        <v>4.0636303292314198</v>
       </c>
       <c r="G33">
-        <v>7398981.9115470499</v>
+        <v>4063630.3292314201</v>
       </c>
       <c r="H33">
-        <v>1.2018402911336219</v>
+        <v>3.3070393593639249</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C34">
-        <v>118276</v>
+        <v>198332</v>
       </c>
       <c r="D34">
-        <v>20011.000000000651</v>
+        <v>79945.000000031156</v>
       </c>
       <c r="E34">
-        <v>5.9105491979409388</v>
+        <v>2.480855588215932</v>
       </c>
       <c r="F34">
-        <v>6.5346297758702052</v>
+        <v>5.2263205778750983</v>
       </c>
       <c r="G34">
-        <v>6534629.7758702049</v>
+        <v>5226320.5778750982</v>
       </c>
       <c r="H34">
-        <v>1.1055875785868901</v>
+        <v>2.106660541911479</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C35">
-        <v>613009</v>
+        <v>378379</v>
       </c>
       <c r="D35">
-        <v>104820.0000000031</v>
+        <v>129313.0000000104</v>
       </c>
       <c r="E35">
-        <v>5.8482064491507506</v>
+        <v>2.9260708513449498</v>
       </c>
       <c r="F35">
-        <v>14.72133604200166</v>
+        <v>7.7750435499853063</v>
       </c>
       <c r="G35">
-        <v>14721336.042001661</v>
+        <v>7775043.5499853063</v>
       </c>
       <c r="H35">
-        <v>2.517239459653382</v>
+        <v>2.657161752051068</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C36">
-        <v>808476</v>
+        <v>160623</v>
       </c>
       <c r="D36">
-        <v>138844.00000002471</v>
+        <v>187915.00000000509</v>
       </c>
       <c r="E36">
-        <v>5.8229091642408459</v>
+        <v>0.85476412207644759</v>
       </c>
       <c r="F36">
-        <v>11.076245402720311</v>
+        <v>10.855665306454499</v>
       </c>
       <c r="G36">
-        <v>11076245.40272031</v>
+        <v>10855665.3064545</v>
       </c>
       <c r="H36">
-        <v>1.902184130011989</v>
+        <v>12.70018830467899</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C37">
-        <v>4825230</v>
+        <v>305020</v>
       </c>
       <c r="D37">
-        <v>858764</v>
+        <v>105992.00000002451</v>
       </c>
       <c r="E37">
-        <v>5.6188079612093658</v>
+        <v>2.8777643595736428</v>
       </c>
       <c r="F37">
-        <v>24.090047639507091</v>
+        <v>7.2182197322948358</v>
       </c>
       <c r="G37">
-        <v>24090047.639507089</v>
+        <v>7218219.7322948361</v>
       </c>
       <c r="H37">
-        <v>4.2873947295970698</v>
+        <v>2.5082733783541111</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C38">
-        <v>752017</v>
+        <v>81338</v>
       </c>
       <c r="D38">
-        <v>167410.0000000119</v>
+        <v>41813.000000002947</v>
       </c>
       <c r="E38">
-        <v>4.4920673794871657</v>
+        <v>1.945280176021674</v>
       </c>
       <c r="F38">
-        <v>8.2079834688570958</v>
+        <v>3.1009326941548951</v>
       </c>
       <c r="G38">
-        <v>8207983.4688570956</v>
+        <v>3100932.6941548949</v>
       </c>
       <c r="H38">
-        <v>1.8272173534926259</v>
+        <v>1.5940802422079201</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C39">
-        <v>1285134</v>
+        <v>744311</v>
       </c>
       <c r="D39">
-        <v>324942.99999999697</v>
+        <v>75234.938746999134</v>
       </c>
       <c r="E39">
-        <v>3.954952099291297</v>
+        <v>9.8931561904101102</v>
       </c>
       <c r="F39">
-        <v>19.72282493630215</v>
+        <v>14.622708703082379</v>
       </c>
       <c r="G39">
-        <v>19722824.936302152</v>
+        <v>14622708.703082381</v>
       </c>
       <c r="H39">
-        <v>4.9868682201830863</v>
+        <v>1.478063059113212</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C40">
-        <v>166605</v>
+        <v>532601</v>
       </c>
       <c r="D40">
-        <v>43874.00000000115</v>
+        <v>79968.000000001339</v>
       </c>
       <c r="E40">
-        <v>3.7973515065869452</v>
+        <v>6.6601765706281402</v>
       </c>
       <c r="F40">
-        <v>7.5473743493451373</v>
+        <v>8.963063922635822</v>
       </c>
       <c r="G40">
-        <v>7547374.3493451374</v>
+        <v>8963063.9226358216</v>
       </c>
       <c r="H40">
-        <v>1.987536401687688</v>
+        <v>1.345769714599397</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C41">
-        <v>444627</v>
+        <v>102497.99157891489</v>
       </c>
       <c r="D41">
-        <v>121217.0000000571</v>
+        <v>231741.35660714979</v>
       </c>
       <c r="E41">
-        <v>3.668025111987514</v>
+        <v>0.44229477672675632</v>
       </c>
       <c r="F41">
-        <v>7.9216015789728083</v>
+        <v>7.169916698404843</v>
       </c>
       <c r="G41">
-        <v>7921601.5789728081</v>
+        <v>7169916.698404843</v>
       </c>
       <c r="H41">
-        <v>2.1596366810805452</v>
+        <v>16.2107198087811</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C42">
-        <v>156442</v>
+        <v>16271.46324615887</v>
       </c>
       <c r="D42">
-        <v>51555.000000003318</v>
+        <v>34484.752941129023</v>
       </c>
       <c r="E42">
-        <v>3.0344680438364842</v>
+        <v>0.47184514483652679</v>
       </c>
       <c r="F42">
-        <v>5.6682965287302336</v>
+        <v>1.4688362713320191</v>
       </c>
       <c r="G42">
-        <v>5668296.5287302341</v>
+        <v>1468836.271332019</v>
       </c>
       <c r="H42">
-        <v>1.867970414202746</v>
+        <v>3.1129625628359601</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C43">
-        <v>378379</v>
+        <v>12467.511832466311</v>
       </c>
       <c r="D43">
-        <v>129313.0000000104</v>
+        <v>16753.73575226765</v>
       </c>
       <c r="E43">
-        <v>2.9260708513449498</v>
+        <v>0.74416309394033542</v>
       </c>
       <c r="F43">
-        <v>7.7750435499853063</v>
+        <v>1.1234416336950019</v>
       </c>
       <c r="G43">
-        <v>7775043.5499853063</v>
+        <v>1123441.6336950019</v>
       </c>
       <c r="H43">
-        <v>2.657161752051068</v>
+        <v>1.5096712573400961</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C44">
-        <v>305020</v>
+        <v>27161.033342459919</v>
       </c>
       <c r="D44">
-        <v>105992.00000002451</v>
+        <v>40159.15469945356</v>
       </c>
       <c r="E44">
-        <v>2.8777643595736428</v>
+        <v>0.67633478706735572</v>
       </c>
       <c r="F44">
-        <v>7.2182197322948358</v>
+        <v>1.3381089256604279</v>
       </c>
       <c r="G44">
-        <v>7218219.7322948361</v>
+        <v>1338108.9256604279</v>
       </c>
       <c r="H44">
-        <v>2.5082733783541111</v>
+        <v>1.9784712412362819</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C45">
-        <v>137454</v>
+        <v>563905</v>
       </c>
       <c r="D45">
-        <v>50175.904170072157</v>
+        <v>82219.993974276586</v>
       </c>
       <c r="E45">
-        <v>2.739442413117203</v>
+        <v>6.8584899212766146</v>
       </c>
       <c r="F45">
-        <v>4.7715573064099273</v>
+        <v>8.9024938057993062</v>
       </c>
       <c r="G45">
-        <v>4771557.3064099271</v>
+        <v>8902493.8057993054</v>
       </c>
       <c r="H45">
-        <v>1.741798726471635</v>
+        <v>1.2980253536834281</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="C46">
-        <v>765202</v>
+        <v>7617875</v>
       </c>
       <c r="D46">
-        <v>292406.00000000309</v>
+        <v>552073.00000004855</v>
       </c>
       <c r="E46">
-        <v>2.616916205549789</v>
+        <v>13.79867336384741</v>
       </c>
       <c r="F46">
-        <v>38.621852550824357</v>
+        <v>38.249635993911859</v>
       </c>
       <c r="G46">
-        <v>38621852.550824367</v>
+        <v>38249635.993911862</v>
       </c>
       <c r="H46">
-        <v>14.758536199560989</v>
+        <v>2.771979232012701</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C47">
-        <v>198332</v>
+        <v>2968849</v>
       </c>
       <c r="D47">
-        <v>79945.000000031156</v>
+        <v>175093.00000000029</v>
       </c>
       <c r="E47">
-        <v>2.480855588215932</v>
+        <v>16.955840610418431</v>
       </c>
       <c r="F47">
-        <v>5.2263205778750983</v>
+        <v>21.756919884595071</v>
       </c>
       <c r="G47">
-        <v>5226320.5778750982</v>
+        <v>21756919.88459507</v>
       </c>
       <c r="H47">
-        <v>2.106660541911479</v>
+        <v>1.2831519465467629</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C48">
-        <v>190956</v>
+        <v>16293655</v>
       </c>
       <c r="D48">
-        <v>78544.000000008746</v>
+        <v>1120579</v>
       </c>
       <c r="E48">
-        <v>2.431197799958988</v>
+        <v>14.54038938798603</v>
       </c>
       <c r="F48">
-        <v>6.3531535615948442</v>
+        <v>44.922939518520081</v>
       </c>
       <c r="G48">
-        <v>6353153.5615948439</v>
+        <v>44922939.51852008</v>
       </c>
       <c r="H48">
-        <v>2.6131783936716362</v>
+        <v>3.0895279569086069</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49">
-        <v>52733</v>
+        <v>4076625</v>
       </c>
       <c r="D49">
-        <v>23042.0000000125</v>
+        <v>398813.04492834641</v>
       </c>
       <c r="E49">
-        <v>2.2885600208302841</v>
+        <v>10.221894824760399</v>
       </c>
       <c r="F49">
-        <v>3.0916204444885649</v>
+        <v>21.240187552044389</v>
       </c>
       <c r="G49">
-        <v>3091620.444488565</v>
+        <v>21240187.552044392</v>
       </c>
       <c r="H49">
-        <v>1.3509020590890739</v>
+        <v>2.0779109857982969</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C50">
-        <v>81338</v>
+        <v>52733</v>
       </c>
       <c r="D50">
-        <v>41813.000000002947</v>
+        <v>23042.0000000125</v>
       </c>
       <c r="E50">
-        <v>1.945280176021674</v>
+        <v>2.2885600208302841</v>
       </c>
       <c r="F50">
-        <v>3.1009326941548951</v>
+        <v>3.0916204444885649</v>
       </c>
       <c r="G50">
-        <v>3100932.6941548949</v>
+        <v>3091620.444488565</v>
       </c>
       <c r="H50">
-        <v>1.5940802422079201</v>
+        <v>1.3509020590890739</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C51">
-        <v>1241143</v>
+        <v>60529</v>
       </c>
       <c r="D51">
-        <v>649009.00000027753</v>
+        <v>44807.000000012849</v>
       </c>
       <c r="E51">
-        <v>1.912366392452908</v>
+        <v>1.3508826745817091</v>
       </c>
       <c r="F51">
-        <v>15.87516756088864</v>
+        <v>2.823031826875094</v>
       </c>
       <c r="G51">
-        <v>15875167.560888641</v>
+        <v>2823031.8268750939</v>
       </c>
       <c r="H51">
-        <v>8.3013211398921616</v>
+        <v>2.089768327030491</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C52">
-        <v>201777</v>
+        <v>808476</v>
       </c>
       <c r="D52">
-        <v>109595.0000000502</v>
+        <v>138844.00000002471</v>
       </c>
       <c r="E52">
-        <v>1.841115014370251</v>
+        <v>5.8229091642408459</v>
       </c>
       <c r="F52">
-        <v>8.1877465356174266</v>
+        <v>11.076245402720311</v>
       </c>
       <c r="G52">
-        <v>8187746.535617427</v>
+        <v>11076245.40272031</v>
       </c>
       <c r="H52">
-        <v>4.4471673261640454</v>
+        <v>1.902184130011989</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C53">
-        <v>98255.000000000015</v>
+        <v>438611</v>
       </c>
       <c r="D53">
-        <v>54637.000000001673</v>
+        <v>27787.00000000565</v>
       </c>
       <c r="E53">
-        <v>1.7983234804252981</v>
+        <v>15.78475546118367</v>
       </c>
       <c r="F53">
-        <v>4.4025505797584703</v>
+        <v>16.746911905795791</v>
       </c>
       <c r="G53">
-        <v>4402550.5797584699</v>
+        <v>16746911.90579579</v>
       </c>
       <c r="H53">
-        <v>2.4481416317365108</v>
+        <v>1.060954789383856</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C54">
-        <v>28949</v>
+        <v>5622208</v>
       </c>
       <c r="D54">
-        <v>18272.999999999829</v>
+        <v>276938.00000003021</v>
       </c>
       <c r="E54">
-        <v>1.584249986318627</v>
+        <v>20.301323761995061</v>
       </c>
       <c r="F54">
-        <v>2.1794480592359018</v>
+        <v>30.069130255861079</v>
       </c>
       <c r="G54">
-        <v>2179448.059235902</v>
+        <v>30069130.255861081</v>
       </c>
       <c r="H54">
-        <v>1.3756970667870141</v>
+        <v>1.4811413584838129</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C55">
-        <v>252106</v>
+        <v>136112</v>
       </c>
       <c r="D55">
-        <v>166879.000000003</v>
+        <v>17903.00000000689</v>
       </c>
       <c r="E55">
-        <v>1.5107113537353141</v>
+        <v>7.6027481427664441</v>
       </c>
       <c r="F55">
-        <v>8.3611184238421021</v>
+        <v>8.6565163276870987</v>
       </c>
       <c r="G55">
-        <v>8361118.4238421023</v>
+        <v>8656516.3276870996</v>
       </c>
       <c r="H55">
-        <v>5.5345572158233889</v>
+        <v>1.1386035897984139</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C56">
-        <v>100208</v>
+        <v>166605</v>
       </c>
       <c r="D56">
-        <v>73148.000000061249</v>
+        <v>43874.00000000115</v>
       </c>
       <c r="E56">
-        <v>1.369934926449337</v>
+        <v>3.7973515065869452</v>
       </c>
       <c r="F56">
-        <v>4.3521505475161097</v>
+        <v>7.5473743493451373</v>
       </c>
       <c r="G56">
-        <v>4352150.5475161094</v>
+        <v>7547374.3493451374</v>
       </c>
       <c r="H56">
-        <v>3.176903124001826</v>
+        <v>1.987536401687688</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C57">
-        <v>104114</v>
+        <v>252106</v>
       </c>
       <c r="D57">
-        <v>76244.0000000078</v>
+        <v>166879.000000003</v>
       </c>
       <c r="E57">
-        <v>1.3655369602852601</v>
+        <v>1.5107113537353141</v>
       </c>
       <c r="F57">
-        <v>3.695716468085589</v>
+        <v>8.3611184238421021</v>
       </c>
       <c r="G57">
-        <v>3695716.4680855889</v>
+        <v>8361118.4238421023</v>
       </c>
       <c r="H57">
-        <v>2.7064199472957191</v>
+        <v>5.5345572158233889</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C58">
-        <v>60529</v>
+        <v>752017</v>
       </c>
       <c r="D58">
-        <v>44807.000000012849</v>
+        <v>167410.0000000119</v>
       </c>
       <c r="E58">
-        <v>1.3508826745817091</v>
+        <v>4.4920673794871657</v>
       </c>
       <c r="F58">
-        <v>2.823031826875094</v>
+        <v>8.2079834688570958</v>
       </c>
       <c r="G58">
-        <v>2823031.8268750939</v>
+        <v>8207983.4688570956</v>
       </c>
       <c r="H58">
-        <v>2.089768327030491</v>
+        <v>1.8272173534926259</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C59">
-        <v>127233</v>
+        <v>1241143</v>
       </c>
       <c r="D59">
-        <v>103544.000000003</v>
+        <v>649009.00000027753</v>
       </c>
       <c r="E59">
-        <v>1.2287819670864211</v>
+        <v>1.912366392452908</v>
       </c>
       <c r="F59">
-        <v>4.0636303292314198</v>
+        <v>15.87516756088864</v>
       </c>
       <c r="G59">
-        <v>4063630.3292314201</v>
+        <v>15875167.560888641</v>
       </c>
       <c r="H59">
-        <v>3.3070393593639249</v>
+        <v>8.3013211398921616</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C60">
-        <v>17784</v>
+        <v>466409</v>
       </c>
       <c r="D60">
-        <v>15694.00000000024</v>
+        <v>639752.00000451563</v>
       </c>
       <c r="E60">
-        <v>1.133171912832913</v>
+        <v>0.72904656803997159</v>
       </c>
       <c r="F60">
-        <v>1.885871726459279</v>
+        <v>3.368000344446973</v>
       </c>
       <c r="G60">
-        <v>1885871.726459279</v>
+        <v>3368000.3444469729</v>
       </c>
       <c r="H60">
-        <v>1.664241502195928</v>
+        <v>4.6197328018452666</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C61">
-        <v>85311</v>
+        <v>1887743</v>
       </c>
       <c r="D61">
-        <v>88307.86977582956</v>
+        <v>228613.00000000559</v>
       </c>
       <c r="E61">
-        <v>0.96606338955477977</v>
+        <v>8.2573738151371661</v>
       </c>
       <c r="F61">
-        <v>3.7180230750651639</v>
+        <v>13.45227843684072</v>
       </c>
       <c r="G61">
-        <v>3718023.0750651639</v>
+        <v>13452278.43684072</v>
       </c>
       <c r="H61">
-        <v>3.8486326210732948</v>
+        <v>1.6291231011221039</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C62">
-        <v>160623</v>
+        <v>630552</v>
       </c>
       <c r="D62">
-        <v>187915.00000000509</v>
+        <v>62891.000000023807</v>
       </c>
       <c r="E62">
-        <v>0.85476412207644759</v>
+        <v>10.026108664192989</v>
       </c>
       <c r="F62">
-        <v>10.855665306454499</v>
+        <v>11.67074224051405</v>
       </c>
       <c r="G62">
-        <v>10855665.3064545</v>
+        <v>11670742.240514049</v>
       </c>
       <c r="H62">
-        <v>12.70018830467899</v>
+        <v>1.164035083939861</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="C63">
-        <v>122810</v>
+        <v>613009</v>
       </c>
       <c r="D63">
-        <v>150065.03251769711</v>
+        <v>104820.0000000031</v>
       </c>
       <c r="E63">
-        <v>0.81837852522716836</v>
+        <v>5.8482064491507506</v>
       </c>
       <c r="F63">
-        <v>7.2253552226546507</v>
+        <v>14.72133604200166</v>
       </c>
       <c r="G63">
-        <v>7225355.2226546509</v>
+        <v>14721336.042001661</v>
       </c>
       <c r="H63">
-        <v>8.8288670828074469</v>
+        <v>2.517239459653382</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C64">
-        <v>12467.511832466311</v>
+        <v>298455</v>
       </c>
       <c r="D64">
-        <v>16753.73575226765</v>
+        <v>48479.000000053493</v>
       </c>
       <c r="E64">
-        <v>0.74416309394033542</v>
+        <v>6.1563769879673824</v>
       </c>
       <c r="F64">
-        <v>1.1234416336950019</v>
+        <v>7.3989819115470503</v>
       </c>
       <c r="G64">
-        <v>1123441.6336950019</v>
+        <v>7398981.9115470499</v>
       </c>
       <c r="H64">
-        <v>1.5096712573400961</v>
+        <v>1.2018402911336219</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C65">
-        <v>466409</v>
+        <v>4178701</v>
       </c>
       <c r="D65">
-        <v>639752.00000451563</v>
+        <v>261715.00000003359</v>
       </c>
       <c r="E65">
-        <v>0.72904656803997159</v>
+        <v>15.966608715585521</v>
       </c>
       <c r="F65">
-        <v>3.368000344446973</v>
+        <v>21.873105311559542</v>
       </c>
       <c r="G65">
-        <v>3368000.3444469729</v>
+        <v>21873105.311559539</v>
       </c>
       <c r="H65">
-        <v>4.6197328018452666</v>
+        <v>1.36992806056608</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C66">
-        <v>27161.033342459919</v>
+        <v>781913</v>
       </c>
       <c r="D66">
-        <v>40159.15469945356</v>
+        <v>43096.000000001281</v>
       </c>
       <c r="E66">
-        <v>0.67633478706735572</v>
+        <v>18.14351679970245</v>
       </c>
       <c r="F66">
-        <v>1.3381089256604279</v>
+        <v>18.663456218173771</v>
       </c>
       <c r="G66">
-        <v>1338108.9256604279</v>
+        <v>18663456.218173768</v>
       </c>
       <c r="H66">
-        <v>1.9784712412362819</v>
+        <v>1.028657036241168</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="C67">
-        <v>92285</v>
+        <v>4825230</v>
       </c>
       <c r="D67">
-        <v>179506</v>
+        <v>858764</v>
       </c>
       <c r="E67">
-        <v>0.51410537809321133</v>
+        <v>5.6188079612093658</v>
       </c>
       <c r="F67">
-        <v>5.7260149380359806</v>
+        <v>24.090047639507091</v>
       </c>
       <c r="G67">
-        <v>5726014.9380359817</v>
+        <v>24090047.639507089</v>
       </c>
       <c r="H67">
-        <v>11.13782345415926</v>
+        <v>4.2873947295970698</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C68">
-        <v>16271.46324615887</v>
+        <v>4202039</v>
       </c>
       <c r="D68">
-        <v>34484.752941129023</v>
+        <v>351095.00000001851</v>
       </c>
       <c r="E68">
-        <v>0.47184514483652679</v>
+        <v>11.96838177701129</v>
       </c>
       <c r="F68">
-        <v>1.4688362713320191</v>
+        <v>18.139004115683299</v>
       </c>
       <c r="G68">
-        <v>1468836.271332019</v>
+        <v>18139004.115683291</v>
       </c>
       <c r="H68">
-        <v>3.1129625628359601</v>
+        <v>1.515576997261606</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C69">
-        <v>102497.99157891489</v>
+        <v>2878667</v>
       </c>
       <c r="D69">
-        <v>231741.35660714979</v>
+        <v>143437.0000000103</v>
       </c>
       <c r="E69">
-        <v>0.44229477672675632</v>
+        <v>20.069208084384041</v>
       </c>
       <c r="F69">
-        <v>7.169916698404843</v>
+        <v>23.524790409325259</v>
       </c>
       <c r="G69">
-        <v>7169916.698404843</v>
+        <v>23524790.409325261</v>
       </c>
       <c r="H69">
-        <v>16.2107198087811</v>
+        <v>1.1721832924553719</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="C70">
-        <v>35440</v>
+        <v>2218572</v>
       </c>
       <c r="D70">
-        <v>92326.00000000032</v>
+        <v>202716.0000000016</v>
       </c>
       <c r="E70">
-        <v>0.38385720165500381</v>
+        <v>10.944237258035789</v>
       </c>
       <c r="F70">
-        <v>2.8433857853210549</v>
+        <v>16.386950474223841</v>
       </c>
       <c r="G70">
-        <v>2843385.785321055</v>
+        <v>16386950.474223839</v>
       </c>
       <c r="H70">
-        <v>7.4074050794456161</v>
+        <v>1.497313160146611</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="C71">
-        <v>2617.3804999999988</v>
+        <v>3428002</v>
       </c>
       <c r="D71">
-        <v>10385.862128765169</v>
+        <v>302873.0000000092</v>
       </c>
       <c r="E71">
-        <v>0.25201379216760261</v>
+        <v>11.3182819201444</v>
       </c>
       <c r="F71">
-        <v>0.47391619658489198</v>
+        <v>19.43730073265084</v>
       </c>
       <c r="G71">
-        <v>473916.19658489199</v>
+        <v>19437300.732650839</v>
       </c>
       <c r="H71">
-        <v>1.8805169054783819</v>
+        <v>1.717336683234238</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="C72">
-        <v>50144</v>
+        <v>1122849</v>
       </c>
       <c r="D72">
-        <v>225938</v>
+        <v>40366.000000006599</v>
       </c>
       <c r="E72">
-        <v>0.22193699156405741</v>
+        <v>27.816702175093312</v>
       </c>
       <c r="F72">
-        <v>6.8699275379572038</v>
+        <v>29.432131767383229</v>
       </c>
       <c r="G72">
-        <v>6869927.5379572036</v>
+        <v>29432131.767383229</v>
       </c>
       <c r="H72">
-        <v>30.954405074804061</v>
+        <v>1.058074087363827</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C73">
-        <v>260.65199999999999</v>
+        <v>4502808</v>
       </c>
       <c r="D73">
-        <v>3303.8713821240121</v>
+        <v>171919.00000001461</v>
       </c>
       <c r="E73">
-        <v>7.8892901645714344E-2</v>
+        <v>26.191450625001409</v>
       </c>
       <c r="F73">
-        <v>0.22889457121488879</v>
+        <v>34.493514780164503</v>
       </c>
       <c r="G73">
-        <v>228894.5712148888</v>
+        <v>34493514.780164503</v>
       </c>
       <c r="H73">
-        <v>2.901332901187859</v>
+        <v>1.316976110793888</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="C74">
-        <v>18842.967499999999</v>
+        <v>6563436</v>
       </c>
       <c r="D74">
-        <v>433811.26648911083</v>
+        <v>74451</v>
       </c>
       <c r="E74">
-        <v>4.3435864754040411E-2</v>
+        <v>88.157795059838008</v>
       </c>
       <c r="F74">
-        <v>10.384374421492151</v>
+        <v>88.157795059838008</v>
       </c>
       <c r="G74">
-        <v>10384374.42149215</v>
+        <v>88157795.059838012</v>
       </c>
       <c r="H74">
-        <v>239.07373504118371</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H74" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H74">
-      <sortCondition descending="1" ref="E1:E74"/>
+      <sortCondition ref="A1:A74"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
